--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/1457-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/1457-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{90CE8DDF-62A7-48A8-9AA2-8DD90515F619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8A36CF4-F7CA-4D53-BC1E-DDD5A19DB5CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{67F7C7EC-48D8-4877-B2E3-F16F6E17AA40}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{810797BB-7FA0-4E06-BF9A-E315F7356F6B}"/>
   </bookViews>
   <sheets>
     <sheet name="1457-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1451,25 +1451,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F52353A5-294C-4968-8809-0ED2A51FAADA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B1570E-2967-4A6D-A092-A7EF8F4437C5}">
   <dimension ref="A1:R43"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1497,7 +1497,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1527,7 +1527,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1623,7 +1623,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>5.65</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="39">
         <v>2024</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="37">
         <v>2023</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>5.32</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2022</v>
       </c>
@@ -1839,7 +1839,7 @@
         <v>5.63</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="37">
         <v>2021</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>26</v>
       </c>
@@ -1949,7 +1949,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="39">
         <v>2020</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>7.81</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>26</v>
       </c>
@@ -2059,7 +2059,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>26</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>4.24</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="37">
         <v>2019</v>
       </c>
@@ -2169,7 +2169,7 @@
         <v>8.35</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>26</v>
       </c>
@@ -2225,7 +2225,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>26</v>
       </c>
@@ -2281,7 +2281,7 @@
         <v>4.78</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="39">
         <v>2018</v>
       </c>
@@ -2335,7 +2335,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="37">
         <v>2017</v>
       </c>
@@ -2389,7 +2389,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="39">
         <v>2016</v>
       </c>
@@ -2443,7 +2443,7 @@
         <v>5.66</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="37">
         <v>2015</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="39">
         <v>2014</v>
       </c>
@@ -2551,7 +2551,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="37">
         <v>2013</v>
       </c>
@@ -2605,7 +2605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="39">
         <v>2012</v>
       </c>
@@ -2659,7 +2659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="37">
         <v>2011</v>
       </c>
@@ -2713,7 +2713,7 @@
         <v>5.54</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="39">
         <v>2010</v>
       </c>
@@ -2767,7 +2767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="37">
         <v>2009</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="39">
         <v>2008</v>
       </c>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="37">
         <v>2007</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="39">
         <v>2006</v>
       </c>
@@ -2983,7 +2983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="37">
         <v>2005</v>
       </c>
@@ -3037,7 +3037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="39">
         <v>2004</v>
       </c>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="37">
         <v>2003</v>
       </c>
@@ -3145,7 +3145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="39">
         <v>2002</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="37">
         <v>2001</v>
       </c>
@@ -3253,7 +3253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="39">
         <v>2000</v>
       </c>
@@ -3307,7 +3307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="37">
         <v>1999</v>
       </c>
@@ -3361,7 +3361,7 @@
         <v>9.6300000000000008</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="39">
         <v>1998</v>
       </c>
@@ -3415,7 +3415,7 @@
         <v>5.95</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="37">
         <v>1997</v>
       </c>
@@ -3469,7 +3469,7 @@
         <v>6.71</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="39">
         <v>1996</v>
       </c>
@@ -3523,7 +3523,7 @@
         <v>5.86</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="37">
         <v>1995</v>
       </c>
@@ -3577,7 +3577,7 @@
         <v>5.22</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="39">
         <v>1994</v>
       </c>
@@ -3631,7 +3631,7 @@
         <v>3.31</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="37">
         <v>1993</v>
       </c>
@@ -3685,7 +3685,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="39" t="s">
         <v>36</v>
       </c>
